--- a/artfynd/A 4333-2026 artfynd.xlsx
+++ b/artfynd/A 4333-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>119109576</v>
       </c>
       <c r="B2" t="n">
-        <v>90544</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119109581</v>
+        <v>119109598</v>
       </c>
       <c r="B3" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dalåsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453877</v>
+        <v>453918</v>
       </c>
       <c r="R3" t="n">
-        <v>6964487</v>
+        <v>6964362</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1,7 m ovan mark.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119109585</v>
+        <v>119109577</v>
       </c>
       <c r="B4" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,20 +898,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dalåsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453610</v>
+        <v>453893</v>
       </c>
       <c r="R4" t="n">
-        <v>6964641</v>
+        <v>6964365</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +944,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,12 +974,7 @@
         <v>119109578</v>
       </c>
       <c r="B5" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,15 +1077,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119109580</v>
+        <v>119109579</v>
       </c>
       <c r="B6" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453804</v>
+        <v>453814</v>
       </c>
       <c r="R6" t="n">
-        <v>6964782</v>
+        <v>6964777</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,15 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119109593</v>
+        <v>119109580</v>
       </c>
       <c r="B7" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454052</v>
+        <v>453804</v>
       </c>
       <c r="R7" t="n">
-        <v>6964383</v>
+        <v>6964782</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,15 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119109588</v>
+        <v>119109581</v>
       </c>
       <c r="B8" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1320,11 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1380,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453605</v>
+        <v>453877</v>
       </c>
       <c r="R8" t="n">
-        <v>6964465</v>
+        <v>6964487</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,7 +1372,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>1,7 m ovan mark.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,15 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119109597</v>
+        <v>119109582</v>
       </c>
       <c r="B9" t="n">
-        <v>57461</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,34 +1410,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Dalåsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>453859</v>
+        <v>453866</v>
       </c>
       <c r="R9" t="n">
-        <v>6964743</v>
+        <v>6964466</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,6 +1474,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,15 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119109600</v>
+        <v>119109583</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,34 +1516,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dalåsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>453858</v>
+        <v>453773</v>
       </c>
       <c r="R10" t="n">
-        <v>6964742</v>
+        <v>6964474</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,6 +1580,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,12 +1614,7 @@
         <v>119109584</v>
       </c>
       <c r="B11" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,15 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119109602</v>
+        <v>119109585</v>
       </c>
       <c r="B12" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,34 +1728,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dalåsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>453800</v>
+        <v>453610</v>
       </c>
       <c r="R12" t="n">
-        <v>6964897</v>
+        <v>6964641</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1838,6 +1792,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,15 +1823,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119109592</v>
+        <v>119109587</v>
       </c>
       <c r="B13" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454051</v>
+        <v>453547</v>
       </c>
       <c r="R13" t="n">
-        <v>6964315</v>
+        <v>6964646</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,15 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119109596</v>
+        <v>119109588</v>
       </c>
       <c r="B14" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2019,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>453711</v>
+        <v>453605</v>
       </c>
       <c r="R14" t="n">
-        <v>6964944</v>
+        <v>6964465</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2008,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,15 +2035,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119109591</v>
+        <v>119109589</v>
       </c>
       <c r="B15" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454034</v>
+        <v>453890</v>
       </c>
       <c r="R15" t="n">
-        <v>6964314</v>
+        <v>6964332</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2197,15 +2141,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119109598</v>
+        <v>119109590</v>
       </c>
       <c r="B16" t="n">
-        <v>90564</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,34 +2152,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dalåsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>453918</v>
+        <v>453896</v>
       </c>
       <c r="R16" t="n">
-        <v>6964362</v>
+        <v>6964358</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,6 +2216,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2299,15 +2247,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119109589</v>
+        <v>119109591</v>
       </c>
       <c r="B17" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,10 +2286,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>453890</v>
+        <v>454034</v>
       </c>
       <c r="R17" t="n">
-        <v>6964332</v>
+        <v>6964314</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2410,15 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119109582</v>
+        <v>119109592</v>
       </c>
       <c r="B18" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>453866</v>
+        <v>454051</v>
       </c>
       <c r="R18" t="n">
-        <v>6964466</v>
+        <v>6964315</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2521,15 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119109601</v>
+        <v>119109593</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2537,34 +2470,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Dalåsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>453845</v>
+        <v>454052</v>
       </c>
       <c r="R19" t="n">
-        <v>6964803</v>
+        <v>6964383</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2597,6 +2534,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2626,12 +2568,7 @@
         <v>119109594</v>
       </c>
       <c r="B20" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2734,15 +2671,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119109579</v>
+        <v>119109595</v>
       </c>
       <c r="B21" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2778,10 +2710,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>453814</v>
+        <v>453854</v>
       </c>
       <c r="R21" t="n">
-        <v>6964777</v>
+        <v>6964767</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2818,7 +2750,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,15 +2777,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119109587</v>
+        <v>119109596</v>
       </c>
       <c r="B22" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2889,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>453547</v>
+        <v>453711</v>
       </c>
       <c r="R22" t="n">
-        <v>6964646</v>
+        <v>6964944</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2956,15 +2883,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119109577</v>
+        <v>119109597</v>
       </c>
       <c r="B23" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2972,21 +2894,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2996,10 +2918,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>453893</v>
+        <v>453859</v>
       </c>
       <c r="R23" t="n">
-        <v>6964365</v>
+        <v>6964743</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,11 +2956,6 @@
           <t>2024-08-12</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3060,441 +2977,6 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>119109599</v>
-      </c>
-      <c r="B24" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Dalåsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>453950</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6964464</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Myssjö</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>119109583</v>
-      </c>
-      <c r="B25" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Dalåsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>453773</v>
-      </c>
-      <c r="R25" t="n">
-        <v>6964474</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Myssjö</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>119109595</v>
-      </c>
-      <c r="B26" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Dalåsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>453854</v>
-      </c>
-      <c r="R26" t="n">
-        <v>6964767</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Myssjö</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>119109590</v>
-      </c>
-      <c r="B27" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Dalåsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>453896</v>
-      </c>
-      <c r="R27" t="n">
-        <v>6964358</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Myssjö</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4333-2026 artfynd.xlsx
+++ b/artfynd/A 4333-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109576</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109598</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109577</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109578</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109579</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109580</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109581</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1502,6 +1542,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109582</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1608,6 +1653,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109583</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1714,6 +1764,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109584</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1820,6 +1875,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109585</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1926,6 +1986,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109587</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2032,6 +2097,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109588</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2138,6 +2208,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109589</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2244,6 +2319,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109590</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2350,6 +2430,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109591</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2456,6 +2541,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109592</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2562,6 +2652,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109593</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2668,6 +2763,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109594</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2774,6 +2874,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109595</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2880,6 +2985,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109596</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2977,8 +3087,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119109597</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>